--- a/doc/조사메뉴 설계.xlsx
+++ b/doc/조사메뉴 설계.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725"/>
+    <workbookView xWindow="390" yWindow="600" windowWidth="9375" windowHeight="13725" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="크롤링분석" sheetId="8" r:id="rId1"/>
@@ -577,10 +577,6 @@
   </si>
   <si>
     <t>상태</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>search_status</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
@@ -880,6 +876,10 @@
   </si>
   <si>
     <t>옥션</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>josa_status</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -4542,59 +4542,59 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1136">
@@ -5979,7 +5979,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1133475" y="14439900"/>
+          <a:off x="1133475" y="15982950"/>
           <a:ext cx="9307225" cy="1819529"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -7275,17 +7275,17 @@
     </row>
     <row r="6" spans="1:3" ht="121.5" x14ac:dyDescent="0.2">
       <c r="A6" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="26" t="s">
         <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -7296,7 +7296,7 @@
       </c>
     </row>
     <row r="8" spans="1:3" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="26"/>
       <c r="B8" s="3" t="s">
         <v>11</v>
       </c>
@@ -7305,7 +7305,7 @@
       </c>
     </row>
     <row r="9" spans="1:3" ht="121.5" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="26"/>
       <c r="B9" s="3" t="s">
         <v>5</v>
       </c>
@@ -7314,7 +7314,7 @@
       </c>
     </row>
     <row r="10" spans="1:3" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A10" s="12"/>
+      <c r="A10" s="26"/>
       <c r="B10" s="3" t="s">
         <v>21</v>
       </c>
@@ -7323,7 +7323,7 @@
       </c>
     </row>
     <row r="11" spans="1:3" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A11" s="12"/>
+      <c r="A11" s="26"/>
       <c r="B11" s="3" t="s">
         <v>22</v>
       </c>
@@ -7332,7 +7332,7 @@
       </c>
     </row>
     <row r="12" spans="1:3" ht="256.5" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
+      <c r="A12" s="26"/>
       <c r="B12" s="3" t="s">
         <v>6</v>
       </c>
@@ -7341,7 +7341,7 @@
       </c>
     </row>
     <row r="13" spans="1:3" ht="40.5" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
+      <c r="A13" s="26"/>
       <c r="B13" s="3" t="s">
         <v>14</v>
       </c>
@@ -7357,7 +7357,7 @@
         <v>23</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.2">
@@ -7372,7 +7372,7 @@
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="27" t="s">
         <v>53</v>
       </c>
       <c r="B16" s="10" t="s">
@@ -7383,7 +7383,7 @@
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="11" t="s">
         <v>26</v>
       </c>
@@ -7392,7 +7392,7 @@
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="11" t="s">
         <v>27</v>
       </c>
@@ -7401,7 +7401,7 @@
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="11" t="s">
         <v>39</v>
       </c>
@@ -7410,7 +7410,7 @@
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A20" s="13"/>
+      <c r="A20" s="27"/>
       <c r="B20" s="11" t="s">
         <v>28</v>
       </c>
@@ -7419,7 +7419,7 @@
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A21" s="13"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="11" t="s">
         <v>32</v>
       </c>
@@ -7428,7 +7428,7 @@
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A22" s="13"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="11" t="s">
         <v>33</v>
       </c>
@@ -7437,7 +7437,7 @@
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A23" s="13"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="11" t="s">
         <v>34</v>
       </c>
@@ -7446,7 +7446,7 @@
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A24" s="13"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="11" t="s">
         <v>49</v>
       </c>
@@ -7455,7 +7455,7 @@
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A25" s="13"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="11" t="s">
         <v>29</v>
       </c>
@@ -7464,7 +7464,7 @@
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A26" s="13"/>
+      <c r="A26" s="27"/>
       <c r="B26" s="11" t="s">
         <v>45</v>
       </c>
@@ -7473,7 +7473,7 @@
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A27" s="13"/>
+      <c r="A27" s="27"/>
       <c r="B27" s="11" t="s">
         <v>31</v>
       </c>
@@ -7507,7 +7507,7 @@
   <dimension ref="A2:F66"/>
   <sheetFormatPr defaultColWidth="17" defaultRowHeight="18" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="17" style="15"/>
+    <col min="1" max="2" width="17" style="13"/>
     <col min="3" max="3" width="26.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="17" style="1"/>
     <col min="5" max="5" width="69.28515625" style="1" customWidth="1"/>
@@ -7522,145 +7522,145 @@
       </c>
     </row>
     <row r="4" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C4" s="21" t="s">
-        <v>112</v>
+      <c r="C4" s="19" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="5" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C5" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>115</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>116</v>
       </c>
     </row>
     <row r="7" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>106</v>
-      </c>
     </row>
     <row r="10" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="19" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="11" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B11" s="15" t="s">
-        <v>113</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>118</v>
+      <c r="B11" s="13" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="12" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B12" s="15" t="s">
-        <v>113</v>
+      <c r="B12" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="13" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B13" s="15" t="s">
-        <v>113</v>
+      <c r="B13" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="14" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="15" t="s">
-        <v>113</v>
+      <c r="B14" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="15" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B15" s="15" t="s">
-        <v>113</v>
+      <c r="B15" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C15" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D15" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D15" s="1" t="s">
-        <v>104</v>
-      </c>
     </row>
     <row r="16" spans="2:4" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B16" s="15" t="s">
-        <v>113</v>
+      <c r="B16" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B17" s="15" t="s">
-        <v>113</v>
+      <c r="B17" s="13" t="s">
+        <v>112</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B19" s="15" t="s">
-        <v>114</v>
+      <c r="B19" s="13" t="s">
+        <v>113</v>
       </c>
       <c r="C19" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B20" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C20" s="1" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B20" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="D20" s="1" t="s">
+    </row>
+    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B21" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="1" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B21" s="15" t="s">
-        <v>114</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>110</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="26" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="21" t="s">
+      <c r="C26" s="19" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="21" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="B27" s="24" t="s">
-        <v>101</v>
-      </c>
-      <c r="C27" s="16" t="s">
+      <c r="B27" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="14" t="s">
         <v>62</v>
       </c>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="E27" s="16" t="s">
-        <v>100</v>
-      </c>
-      <c r="F27" s="16" t="s">
+      <c r="E27" s="14" t="s">
+        <v>99</v>
+      </c>
+      <c r="F27" s="14" t="s">
         <v>91</v>
       </c>
     </row>
@@ -7670,11 +7670,11 @@
       <c r="C28" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D28" s="17" t="s">
+      <c r="D28" s="15" t="s">
         <v>95</v>
       </c>
       <c r="E28" s="3"/>
-      <c r="F28" s="18" t="s">
+      <c r="F28" s="16" t="s">
         <v>94</v>
       </c>
     </row>
@@ -7684,12 +7684,12 @@
       <c r="C29" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D29" s="17" t="s">
-        <v>99</v>
+      <c r="D29" s="15" t="s">
+        <v>132</v>
       </c>
       <c r="E29" s="3"/>
       <c r="F29" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="13.5" x14ac:dyDescent="0.2">
@@ -7700,13 +7700,13 @@
         <v>18</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="D30" s="17" t="s">
+        <v>131</v>
+      </c>
+      <c r="D30" s="15" t="s">
         <v>75</v>
       </c>
       <c r="E30" s="3"/>
-      <c r="F30" s="18" t="s">
+      <c r="F30" s="16" t="s">
         <v>92</v>
       </c>
     </row>
@@ -7720,13 +7720,13 @@
       <c r="C31" s="11" t="s">
         <v>67</v>
       </c>
-      <c r="D31" s="19" t="s">
+      <c r="D31" s="17" t="s">
         <v>63</v>
       </c>
       <c r="E31" s="10" t="s">
         <v>54</v>
       </c>
-      <c r="F31" s="18" t="s">
+      <c r="F31" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -7740,13 +7740,13 @@
       <c r="C32" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="17" t="s">
         <v>64</v>
       </c>
       <c r="E32" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="F32" s="18" t="s">
+      <c r="F32" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -7758,13 +7758,13 @@
       <c r="C33" s="11" t="s">
         <v>88</v>
       </c>
-      <c r="D33" s="19" t="s">
+      <c r="D33" s="17" t="s">
         <v>65</v>
       </c>
       <c r="E33" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="F33" s="18" t="s">
+      <c r="F33" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -7784,7 +7784,7 @@
       <c r="E34" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F34" s="14"/>
+      <c r="F34" s="12"/>
     </row>
     <row r="35" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A35" s="6">
@@ -7802,7 +7802,7 @@
       <c r="E35" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="F35" s="14"/>
+      <c r="F35" s="12"/>
     </row>
     <row r="36" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A36" s="6"/>
@@ -7818,7 +7818,7 @@
       <c r="E36" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="F36" s="14"/>
+      <c r="F36" s="12"/>
     </row>
     <row r="37" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="6"/>
@@ -7834,7 +7834,7 @@
       <c r="E37" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="F37" s="14"/>
+      <c r="F37" s="12"/>
     </row>
     <row r="38" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="6">
@@ -7852,7 +7852,7 @@
       <c r="E38" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="F38" s="14"/>
+      <c r="F38" s="12"/>
     </row>
     <row r="39" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="6">
@@ -7870,7 +7870,7 @@
       <c r="E39" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="F39" s="14"/>
+      <c r="F39" s="12"/>
     </row>
     <row r="40" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="6">
@@ -7888,7 +7888,7 @@
       <c r="E40" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="F40" s="14"/>
+      <c r="F40" s="12"/>
     </row>
     <row r="41" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="6">
@@ -7906,7 +7906,7 @@
       <c r="E41" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="F41" s="14"/>
+      <c r="F41" s="12"/>
     </row>
     <row r="42" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A42" s="6"/>
@@ -7916,11 +7916,11 @@
       <c r="C42" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="D42" s="17" t="s">
+      <c r="D42" s="15" t="s">
         <v>76</v>
       </c>
       <c r="E42" s="3"/>
-      <c r="F42" s="20"/>
+      <c r="F42" s="18"/>
     </row>
     <row r="43" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A43" s="6"/>
@@ -7930,11 +7930,11 @@
       <c r="C43" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D43" s="17" t="s">
+      <c r="D43" s="15" t="s">
         <v>77</v>
       </c>
       <c r="E43" s="3"/>
-      <c r="F43" s="20"/>
+      <c r="F43" s="18"/>
     </row>
     <row r="44" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A44" s="6"/>
@@ -7948,7 +7948,7 @@
         <v>80</v>
       </c>
       <c r="E44" s="3"/>
-      <c r="F44" s="18"/>
+      <c r="F44" s="16"/>
     </row>
     <row r="45" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A45" s="6"/>
@@ -7958,11 +7958,11 @@
       <c r="C45" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="17" t="s">
+      <c r="D45" s="15" t="s">
         <v>78</v>
       </c>
       <c r="E45" s="3"/>
-      <c r="F45" s="20"/>
+      <c r="F45" s="18"/>
     </row>
     <row r="46" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A46" s="6"/>
@@ -7972,11 +7972,11 @@
       <c r="C46" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="D46" s="17" t="s">
+      <c r="D46" s="15" t="s">
         <v>79</v>
       </c>
       <c r="E46" s="3"/>
-      <c r="F46" s="20"/>
+      <c r="F46" s="18"/>
     </row>
     <row r="47" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A47" s="6">
@@ -7984,29 +7984,29 @@
       </c>
       <c r="B47" s="6"/>
       <c r="C47" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-      <c r="F47" s="29" t="s">
-        <v>130</v>
+      <c r="F47" s="25" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A48" s="6"/>
       <c r="B48" s="6"/>
       <c r="C48" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>122</v>
-      </c>
       <c r="E48" s="3"/>
-      <c r="F48" s="20"/>
+      <c r="F48" s="18"/>
     </row>
     <row r="49" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A49" s="6"/>
-      <c r="B49" s="25">
+      <c r="B49" s="22">
         <v>1</v>
       </c>
       <c r="C49" s="3" t="s">
@@ -8014,9 +8014,9 @@
       </c>
       <c r="D49" s="3"/>
       <c r="E49" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F49" s="18" t="s">
+        <v>122</v>
+      </c>
+      <c r="F49" s="16" t="s">
         <v>89</v>
       </c>
     </row>
@@ -8026,68 +8026,68 @@
       </c>
       <c r="B50" s="6"/>
       <c r="C50" s="28" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D50" s="28"/>
       <c r="E50" s="28"/>
-      <c r="F50" s="27"/>
+      <c r="F50" s="24"/>
     </row>
     <row r="51" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="26"/>
+      <c r="A51" s="23"/>
       <c r="C51" s="1" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="52" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="26"/>
+      <c r="A52" s="23"/>
     </row>
     <row r="53" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="26"/>
+      <c r="A53" s="23"/>
     </row>
     <row r="54" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="26"/>
-      <c r="B54" s="15" t="s">
-        <v>129</v>
+      <c r="A54" s="23"/>
+      <c r="B54" s="13" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="26"/>
+      <c r="A55" s="23"/>
     </row>
     <row r="56" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="26"/>
+      <c r="A56" s="23"/>
     </row>
     <row r="57" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="26"/>
+      <c r="A57" s="23"/>
     </row>
     <row r="58" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="26"/>
+      <c r="A58" s="23"/>
     </row>
     <row r="59" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="26"/>
+      <c r="A59" s="23"/>
     </row>
     <row r="60" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="26"/>
+      <c r="A60" s="23"/>
     </row>
     <row r="61" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="26"/>
+      <c r="A61" s="23"/>
     </row>
     <row r="62" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="26"/>
+      <c r="A62" s="23"/>
     </row>
     <row r="63" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="26"/>
+      <c r="A63" s="23"/>
     </row>
     <row r="64" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="26"/>
+      <c r="A64" s="23"/>
     </row>
     <row r="65" spans="1:5" ht="164.25" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A65" s="1"/>
       <c r="B65" s="1"/>
     </row>
     <row r="66" spans="1:5" ht="120.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C66" s="23"/>
-      <c r="D66" s="23"/>
-      <c r="E66" s="23"/>
+      <c r="C66" s="29"/>
+      <c r="D66" s="29"/>
+      <c r="E66" s="29"/>
     </row>
   </sheetData>
   <autoFilter ref="C50">
@@ -8223,20 +8223,20 @@
         <v>86</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="3" spans="1:18" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="19" t="s">
+      <c r="B3" s="17" t="s">
         <v>63</v>
       </c>
-      <c r="C3" s="19" t="s">
+      <c r="C3" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="17" t="s">
         <v>65</v>
       </c>
       <c r="E3" s="11" t="s">
@@ -8263,22 +8263,22 @@
       <c r="L3" s="11" t="s">
         <v>74</v>
       </c>
-      <c r="M3" s="17" t="s">
+      <c r="M3" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="N3" s="17" t="s">
+      <c r="N3" s="15" t="s">
         <v>77</v>
       </c>
       <c r="O3" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="P3" s="17" t="s">
+      <c r="P3" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="Q3" s="17" t="s">
+      <c r="Q3" s="15" t="s">
         <v>79</v>
       </c>
-      <c r="R3" s="17" t="s">
+      <c r="R3" s="15" t="s">
         <v>75</v>
       </c>
     </row>
